--- a/data/기초자료_6차.xlsx
+++ b/data/기초자료_6차.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\본부투자_결재 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BD3DA1-3CC3-4678-AE33-CF2408E16446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0263F22B-75A5-49CA-818A-F08C9114BD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" tabRatio="706" xr2:uid="{52DB04C7-9C9F-49E4-9549-92AEDDAE85FD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="179">
   <si>
     <t xml:space="preserve">  구간명</t>
   </si>
@@ -491,6 +491,102 @@
   <si>
     <t>수성구</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구간명</t>
+  </si>
+  <si>
+    <t>관리번호</t>
+  </si>
+  <si>
+    <t>분석단계</t>
+  </si>
+  <si>
+    <t>가정용[(전,월)]</t>
+  </si>
+  <si>
+    <t>일반용[MJ/(전,월)]</t>
+  </si>
+  <si>
+    <t>산업용[MJ/(전,월)]</t>
+  </si>
+  <si>
+    <t>연료전지[MJ/(전,월)]</t>
+  </si>
+  <si>
+    <t>열병합[MJ/(전,월)]</t>
+  </si>
+  <si>
+    <t>열전용설비[MJ/(전,월)]</t>
+  </si>
+  <si>
+    <t>수요전수계</t>
+  </si>
+  <si>
+    <t>용도별표준가스소비량합계</t>
+  </si>
+  <si>
+    <t>계</t>
+  </si>
+  <si>
+    <t>시설분담금</t>
+  </si>
+  <si>
+    <t>기타이익(수요가부담공사비등)</t>
+  </si>
+  <si>
+    <t>연간판매량[MJ/년]</t>
+  </si>
+  <si>
+    <t>연간판매액[원/년]</t>
+  </si>
+  <si>
+    <t>연간판매원가[원/년]</t>
+  </si>
+  <si>
+    <t>연간판매수익[원/년]</t>
+  </si>
+  <si>
+    <t>길이(m)</t>
+  </si>
+  <si>
+    <t>배관투자금액(원)</t>
+  </si>
+  <si>
+    <t>주택용</t>
+  </si>
+  <si>
+    <t>주택용외</t>
+  </si>
+  <si>
+    <t>산업용(MJ)</t>
+  </si>
+  <si>
+    <t>연료전지(MJ)</t>
+  </si>
+  <si>
+    <t>열병합(MJ)</t>
+  </si>
+  <si>
+    <t>열전용설비(MJ)</t>
+  </si>
+  <si>
+    <t>계(MJ)</t>
+  </si>
+  <si>
+    <t>회수년수</t>
+  </si>
+  <si>
+    <t>NPV(원)</t>
+  </si>
+  <si>
+    <t>IRR(%)</t>
+  </si>
+  <si>
+    <t>100m환산세대수</t>
+  </si>
+  <si>
+    <t>주택용인입관비배분액</t>
   </si>
 </sst>
 </file>
@@ -1512,69 +1608,73 @@
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="3" max="3" width="24.625" customWidth="1"/>
-    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="21.125" customWidth="1"/>
     <col min="46" max="49" width="11.75" customWidth="1"/>
+    <col min="51" max="51" width="17.875" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="12.375" customWidth="1"/>
+    <col min="63" max="63" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="65" max="66" width="25" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="P1" t="s">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="Y1" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="AA1" t="s">
-        <v>8</v>
+        <v>153</v>
       </c>
       <c r="AC1" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="AE1" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="AG1" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="AH1" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="AS1" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="AT1" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="AX1" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="AY1" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="BL1" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="BM1" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="BN1" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="BO1" t="s">
         <v>20</v>
@@ -1582,10 +1682,10 @@
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.3">
       <c r="F2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
         <v>23</v>
@@ -1612,10 +1712,10 @@
         <v>30</v>
       </c>
       <c r="AH2" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="AK2" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="AY2" t="s">
         <v>33</v>
@@ -1624,34 +1724,34 @@
         <v>34</v>
       </c>
       <c r="BG2" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="BH2" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="BI2" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="BJ2" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="BK2" t="s">
-        <v>39</v>
+        <v>173</v>
       </c>
       <c r="BO2" t="s">
-        <v>40</v>
+        <v>174</v>
       </c>
       <c r="BP2" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="BQ2" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="BR2" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="BS2" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.3">
@@ -1661,6 +1761,9 @@
       <c r="B4" t="s">
         <v>121</v>
       </c>
+      <c r="G4" s="6">
+        <v>158200800</v>
+      </c>
       <c r="H4" t="s">
         <v>45</v>
       </c>
@@ -4228,7 +4331,7 @@
         <v>4</v>
       </c>
       <c r="BP16" s="1">
-        <v>1740264041.9472842</v>
+        <v>1740264041.9472799</v>
       </c>
       <c r="BQ16">
         <v>52.056018389181993</v>
@@ -4253,31 +4356,16 @@
       <c r="BP17" s="1"/>
     </row>
     <row r="18" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="F18" s="1">
-        <f>SUM(F5:F16)</f>
-        <v>1358</v>
-      </c>
-      <c r="G18" s="1">
-        <f>SUM(G5:G16)</f>
-        <v>1126967000</v>
-      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
       <c r="BP18" s="1">
         <f>SUM(BP5:BP16)</f>
-        <v>7327394014.9472847</v>
+        <v>7327394014.9472799</v>
       </c>
     </row>
     <row r="19" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="1">
-        <f t="shared" ref="F19:G21" si="0">F5</f>
-        <v>25</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>63179000</v>
-      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
       <c r="BO19" t="s">
         <v>122</v>
       </c>
@@ -4287,17 +4375,8 @@
       </c>
     </row>
     <row r="20" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="E20" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="1">
-        <f t="shared" si="0"/>
-        <v>470</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>474456000</v>
-      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
       <c r="BO20" t="s">
         <v>127</v>
       </c>
@@ -4307,17 +4386,8 @@
       </c>
     </row>
     <row r="21" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="E21" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="1">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>61362000</v>
-      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="BO21" t="s">
         <v>126</v>
       </c>
@@ -4327,17 +4397,8 @@
       </c>
     </row>
     <row r="22" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="E22" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="1">
-        <f>SUM(F8:F15)</f>
-        <v>656</v>
-      </c>
-      <c r="G22" s="1">
-        <f>SUM(G8:G15)</f>
-        <v>374257000</v>
-      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
       <c r="BO22" t="s">
         <v>124</v>
       </c>
@@ -4347,41 +4408,22 @@
       </c>
     </row>
     <row r="23" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
-        <v>145</v>
-      </c>
-      <c r="F23" s="1">
-        <f>F16</f>
-        <v>172</v>
-      </c>
-      <c r="G23" s="1">
-        <f>G16</f>
-        <v>153713000</v>
-      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
       <c r="BO23" t="s">
         <v>145</v>
       </c>
       <c r="BP23" s="1">
         <f>BP16</f>
-        <v>1740264041.9472842</v>
+        <v>1740264041.9472799</v>
       </c>
     </row>
     <row r="24" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="F24" s="1">
-        <f>SUM(F19:F23)</f>
-        <v>1358</v>
-      </c>
-      <c r="G24" s="1">
-        <f>SUM(G19:G23)</f>
-        <v>1126967000</v>
-      </c>
-      <c r="H24" t="b">
-        <f>G24=G18</f>
-        <v>1</v>
-      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
       <c r="BP24" s="1">
         <f>SUM(BP19:BP23)</f>
-        <v>7327394014.9472847</v>
+        <v>7327394014.9472799</v>
       </c>
       <c r="BQ24" t="b">
         <f>BP24=BP18</f>
@@ -4389,27 +4431,14 @@
       </c>
     </row>
     <row r="25" spans="3:69" x14ac:dyDescent="0.3">
-      <c r="E25" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="5">
-        <f>F18-F22</f>
-        <v>702</v>
-      </c>
-      <c r="G25" s="5">
-        <f>G18-G22</f>
-        <v>752710000</v>
-      </c>
-      <c r="H25" t="b">
-        <f>(G18-G22)=G25</f>
-        <v>1</v>
-      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
       <c r="BO25" t="s">
         <v>143</v>
       </c>
       <c r="BP25" s="5">
         <f>BP18-BP22</f>
-        <v>7662162837.9472847</v>
+        <v>7662162837.9472799</v>
       </c>
       <c r="BQ25" t="b">
         <f>(BP18-BP22)=BP25</f>

--- a/data/기초자료_6차.xlsx
+++ b/data/기초자료_6차.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\본부투자_결재 대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0263F22B-75A5-49CA-818A-F08C9114BD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EC7533-6718-40EE-8E02-8B2C1F261BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" tabRatio="706" xr2:uid="{52DB04C7-9C9F-49E4-9549-92AEDDAE85FD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="178">
   <si>
     <t xml:space="preserve">  구간명</t>
   </si>
@@ -475,10 +475,6 @@
   </si>
   <si>
     <t>이곡동1000-346번지R</t>
-  </si>
-  <si>
-    <t>ROE제외</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>이천동대구연호공공택지</t>
@@ -1620,61 +1616,61 @@
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" t="s">
         <v>147</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>148</v>
-      </c>
-      <c r="E1" t="s">
-        <v>149</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
       <c r="H1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P1" t="s">
         <v>150</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Y1" t="s">
         <v>151</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>152</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>153</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>154</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>155</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>156</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AS1" t="s">
         <v>157</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>158</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>159</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>160</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BL1" t="s">
         <v>161</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>162</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>163</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>164</v>
       </c>
       <c r="BO1" t="s">
         <v>20</v>
@@ -1682,10 +1678,10 @@
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.3">
       <c r="F2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" t="s">
         <v>165</v>
-      </c>
-      <c r="G2" t="s">
-        <v>166</v>
       </c>
       <c r="H2" t="s">
         <v>23</v>
@@ -1712,10 +1708,10 @@
         <v>30</v>
       </c>
       <c r="AH2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK2" t="s">
         <v>167</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>168</v>
       </c>
       <c r="AY2" t="s">
         <v>33</v>
@@ -1724,34 +1720,34 @@
         <v>34</v>
       </c>
       <c r="BG2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BH2" t="s">
         <v>169</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>170</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>171</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>172</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BO2" t="s">
         <v>173</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>174</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>175</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>176</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>177</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.3">
@@ -4276,13 +4272,13 @@
     </row>
     <row r="16" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
         <v>145</v>
       </c>
-      <c r="B16" t="s">
-        <v>146</v>
-      </c>
       <c r="C16" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F16">
         <v>172</v>
@@ -4340,7 +4336,7 @@
         <v>1477.9069767441861</v>
       </c>
     </row>
-    <row r="17" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:68" x14ac:dyDescent="0.3">
       <c r="C17" s="4"/>
       <c r="G17" s="1"/>
       <c r="Q17" s="1"/>
@@ -4355,95 +4351,45 @@
       <c r="BN17" s="1"/>
       <c r="BP17" s="1"/>
     </row>
-    <row r="18" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="BP18" s="1">
-        <f>SUM(BP5:BP16)</f>
-        <v>7327394014.9472799</v>
-      </c>
+      <c r="BP18" s="1"/>
     </row>
-    <row r="19" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="BO19" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP19" s="1">
-        <f>BP5</f>
-        <v>1363230703</v>
-      </c>
+      <c r="BP19" s="1"/>
     </row>
-    <row r="20" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="BO20" t="s">
-        <v>127</v>
-      </c>
-      <c r="BP20" s="1">
-        <f>BP6</f>
-        <v>4558036087</v>
-      </c>
+      <c r="BP20" s="1"/>
     </row>
-    <row r="21" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="BO21" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP21" s="1">
-        <f>BP7</f>
-        <v>632006</v>
-      </c>
+      <c r="BP21" s="1"/>
     </row>
-    <row r="22" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="BO22" t="s">
-        <v>124</v>
-      </c>
-      <c r="BP22" s="1">
-        <f>SUM(BP8:BP15)</f>
-        <v>-334768823</v>
-      </c>
+      <c r="BP22" s="1"/>
     </row>
-    <row r="23" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="BO23" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP23" s="1">
-        <f>BP16</f>
-        <v>1740264041.9472799</v>
-      </c>
+      <c r="BP23" s="1"/>
     </row>
-    <row r="24" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="BP24" s="1">
-        <f>SUM(BP19:BP23)</f>
-        <v>7327394014.9472799</v>
-      </c>
-      <c r="BQ24" t="b">
-        <f>BP24=BP18</f>
-        <v>1</v>
-      </c>
+      <c r="BP24" s="1"/>
     </row>
-    <row r="25" spans="3:69" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:68" x14ac:dyDescent="0.3">
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="BO25" t="s">
-        <v>143</v>
-      </c>
-      <c r="BP25" s="5">
-        <f>BP18-BP22</f>
-        <v>7662162837.9472799</v>
-      </c>
-      <c r="BQ25" t="b">
-        <f>(BP18-BP22)=BP25</f>
-        <v>1</v>
-      </c>
+      <c r="BP25" s="5"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:BS15">
